--- a/cds/mm_germany-5year-cds.xlsx
+++ b/cds/mm_germany-5year-cds.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="600">
   <si>
     <t>Date</t>
   </si>
@@ -1800,6 +1800,21 @@
   </si>
   <si>
     <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
   </si>
 </sst>
 </file>
@@ -2149,7 +2164,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B594"/>
+  <dimension ref="A1:B599"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -6902,6 +6917,46 @@
       </c>
       <c r="B594" s="3">
         <v>9</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2">
+      <c r="A595" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="B595" s="3">
+        <v>9.5825</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2">
+      <c r="A596" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="B596" s="3">
+        <v>9.5801</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2">
+      <c r="A597" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="B597" s="3">
+        <v>11.1104</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2">
+      <c r="A598" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="B598" s="3">
+        <v>11.2772</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2">
+      <c r="A599" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="B599" s="3">
+        <v>10.7043</v>
       </c>
     </row>
   </sheetData>
